--- a/artfynd/A 2067-2024 artfynd.xlsx
+++ b/artfynd/A 2067-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2067-2024 artfynd.xlsx
+++ b/artfynd/A 2067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,215 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118135377</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>588492</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7026615</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118135219</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91774</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>588555</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7026614</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
